--- a/human_resources_forms/002_tech_industry_candidate_skills_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/002_tech_industry_candidate_skills_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'programming',_'label':_'programming',_'type':_'select_one',_'options':_[{'id':_5,_'name':_'programming_language_1',_'label':_'python',_'type':_'select_one',_'options':_[],_'required':_true},_{'id':_6,_'name':_'programming_language_2',_'label':_'java',_'type':_'select_one',_'options':_[],_'required':_true},_{'id':_7,_'name':_'programming_language_3',_'label':_'c++',_'type':_'select_one',_'options':_[],_'required':_false}]}</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'programming', 'label': 'Programming', 'type': 'select_one', 'options': [{'id': 5, 'name': 'programming_language_1', 'label': 'Python', 'type': 'select_one', 'options': [], 'required': True}, {'id': 6, 'name': 'programming_language_2', 'label': 'Java', 'type': 'select_one', 'options': [], 'required': True}, {'id': 7, 'name': 'programming_language_3', 'label': 'C++', 'type': 'select_one', 'options': [], 'required': False}]}</t>
+          <t>Programming</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'soft_skills',_'label':_'soft_skills',_'type':_'select_multiple',_'options':_[{'id':_9,_'name':_'teamwork',_'label':_'teamwork',_'type':_'select_one',_'options':_[],_'required':_false},_{'id':_10,_'name':_'communication',_'label':_'communication',_'type':_'select_one',_'options':_[],_'required':_false},_{'id':_11,_'name':_'time_management',_'label':_'time_management',_'type':_'select_one',_'options':_[],_'required':_false}]}</t>
+          <t>soft_skills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'soft_skills', 'label': 'Soft Skills', 'type': 'select_multiple', 'options': [{'id': 9, 'name': 'teamwork', 'label': 'Teamwork', 'type': 'select_one', 'options': [], 'required': False}, {'id': 10, 'name': 'communication', 'label': 'Communication', 'type': 'select_one', 'options': [], 'required': False}, {'id': 11, 'name': 'time_management', 'label': 'Time Management', 'type': 'select_one', 'options': [], 'required': False}]}</t>
+          <t>Soft Skills</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_true,_'label':_true,_'type':_'select_one',_'options':_[],_'required':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': True, 'label': True, 'type': 'select_one', 'options': [], 'required': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_false,_'label':_false,_'type':_'select_one',_'options':_[],_'required':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': False, 'label': False, 'type': 'select_one', 'options': [], 'required': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_true,_'label':_true,_'type':_'select_one',_'options':_[],_'required':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': True, 'label': True, 'type': 'select_one', 'options': [], 'required': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_false,_'label':_false,_'type':_'select_one',_'options':_[],_'required':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': False, 'label': False, 'type': 'select_one', 'options': [], 'required': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
